--- a/exports/trend_1d/ONGC_full_report.xlsx
+++ b/exports/trend_1d/ONGC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>9.49</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42051</v>
+        <v>42053</v>
       </c>
       <c r="H2" t="n">
-        <v>205.1</v>
+        <v>200.4</v>
       </c>
       <c r="I2" t="n">
         <v>204.3638423867891</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.77</v>
+        <v>-4.02</v>
       </c>
       <c r="L2" t="n">
-        <v>2.75</v>
+        <v>4.19</v>
       </c>
       <c r="M2" t="n">
         <v>1.99</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.73</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42109</v>
+        <v>42110</v>
       </c>
       <c r="H3" t="n">
-        <v>191.1</v>
+        <v>197.4</v>
       </c>
       <c r="I3" t="n">
         <v>196.7716622584537</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K3" t="n">
-        <v>4.64</v>
+        <v>1.5</v>
       </c>
       <c r="L3" t="n">
         <v>3.37</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42122</v>
+        <v>42123</v>
       </c>
       <c r="H4" t="n">
-        <v>185.3</v>
+        <v>184.5</v>
       </c>
       <c r="I4" t="n">
         <v>184.8025437795492</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.13</v>
+        <v>-6.53</v>
       </c>
       <c r="L4" t="n">
         <v>7.19</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>9.1</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42128</v>
+        <v>42129</v>
       </c>
       <c r="H5" t="n">
-        <v>197.85</v>
+        <v>206.15</v>
       </c>
       <c r="I5" t="n">
         <v>200.1597029641081</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.24</v>
+        <v>-11.73</v>
       </c>
       <c r="L5" t="n">
-        <v>7.94</v>
+        <v>12.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="N5" t="n">
         <v>8</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>11.44</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42158</v>
+        <v>42159</v>
       </c>
       <c r="H6" t="n">
-        <v>185.5</v>
+        <v>181.6</v>
       </c>
       <c r="I6" t="n">
         <v>182.5573905990724</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.02</v>
+        <v>-11.91</v>
       </c>
       <c r="L6" t="n">
-        <v>10.43</v>
+        <v>12.25</v>
       </c>
       <c r="M6" t="n">
         <v>3.01</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.71</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42282</v>
+        <v>42283</v>
       </c>
       <c r="H7" t="n">
-        <v>144.85</v>
+        <v>149</v>
       </c>
       <c r="I7" t="n">
         <v>148.2417390236449</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K7" t="n">
-        <v>20.24</v>
+        <v>17.95</v>
       </c>
       <c r="L7" t="n">
         <v>7.27</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>11.28</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42317</v>
+        <v>42318</v>
       </c>
       <c r="H8" t="n">
-        <v>150.2</v>
+        <v>142.6</v>
       </c>
       <c r="I8" t="n">
         <v>144.7843037104435</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8100000000000001</v>
+        <v>-4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>3.09</v>
+        <v>4.73</v>
       </c>
       <c r="M8" t="n">
         <v>2.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.59</v>
+        <v>5.06</v>
       </c>
       <c r="O8" t="n">
         <v>2.87</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>11.77</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42360</v>
+        <v>42361</v>
       </c>
       <c r="H9" t="n">
-        <v>138.95</v>
+        <v>141.9</v>
       </c>
       <c r="I9" t="n">
         <v>139.2082322773964</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K9" t="n">
-        <v>2.56</v>
+        <v>0.49</v>
       </c>
       <c r="L9" t="n">
         <v>4.7</v>
       </c>
       <c r="M9" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
         <v>4.08</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>8.58</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42380.38541666666</v>
+        <v>42381.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>135.85</v>
+        <v>133.35</v>
       </c>
       <c r="I10" t="n">
         <v>134.6734796316276</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>19.38541666666667</v>
+        <v>20.38541666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.26</v>
+        <v>-6.03</v>
       </c>
       <c r="L10" t="n">
-        <v>5.67</v>
+        <v>6.55</v>
       </c>
       <c r="M10" t="n">
         <v>2.76</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42486.38541666666</v>
+        <v>42487.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>129.1</v>
+        <v>133.6</v>
       </c>
       <c r="I11" t="n">
         <v>131.465438349644</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K11" t="n">
-        <v>3.19</v>
+        <v>-0.19</v>
       </c>
       <c r="L11" t="n">
         <v>2.92</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>8.09</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42502.38541666666</v>
+        <v>42503.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>124.3</v>
+        <v>122.75</v>
       </c>
       <c r="I12" t="n">
         <v>122.7974557942134</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.96</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>8.42</v>
+        <v>8.91</v>
       </c>
       <c r="M12" t="n">
         <v>0.48</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.42</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42529.38541666666</v>
+        <v>42530.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>130</v>
+        <v>132.9</v>
       </c>
       <c r="I13" t="n">
         <v>130.9184993600807</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.91</v>
+        <v>-8.27</v>
       </c>
       <c r="L13" t="n">
-        <v>8.51</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M13" t="n">
         <v>1.47</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.05</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42676.38541666666</v>
+        <v>42677.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>167</v>
+        <v>161.2</v>
       </c>
       <c r="I14" t="n">
         <v>161.7078914393221</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K14" t="n">
-        <v>25.66</v>
+        <v>21.29</v>
       </c>
       <c r="L14" t="n">
         <v>6.17</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>10.88</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42704.38541666666</v>
+        <v>42705.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>174.05</v>
+        <v>176</v>
       </c>
       <c r="I15" t="n">
         <v>174.153290815537</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.97</v>
+        <v>-9.18</v>
       </c>
       <c r="L15" t="n">
-        <v>8.84</v>
+        <v>11.6</v>
       </c>
       <c r="M15" t="n">
-        <v>1.74</v>
+        <v>2.13</v>
       </c>
       <c r="N15" t="n">
         <v>2.36</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>7.75</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42726.38541666666</v>
+        <v>42727.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>176.15</v>
+        <v>174.4</v>
       </c>
       <c r="I16" t="n">
         <v>175.2356149230599</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K16" t="n">
-        <v>0.09</v>
+        <v>-0.91</v>
       </c>
       <c r="L16" t="n">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
       <c r="M16" t="n">
         <v>0.71</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42759.38541666666</v>
+        <v>42760.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>182.2</v>
+        <v>185.2</v>
       </c>
       <c r="I17" t="n">
         <v>183.8927920209021</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.47</v>
+        <v>-6.19</v>
       </c>
       <c r="L17" t="n">
         <v>7.25</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>7.26</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42802.38541666666</v>
+        <v>42803.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>174.4</v>
+        <v>171.4</v>
       </c>
       <c r="I18" t="n">
         <v>173.3262304211455</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.83</v>
+        <v>-7.45</v>
       </c>
       <c r="L18" t="n">
-        <v>6.88</v>
+        <v>7.72</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="N18" t="n">
         <v>2.86</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.98</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42853.38541666666</v>
+        <v>42857.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>168.6</v>
+        <v>173.9</v>
       </c>
       <c r="I19" t="n">
         <v>169.6447310522517</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K19" t="n">
-        <v>1.63</v>
+        <v>-1.46</v>
       </c>
       <c r="L19" t="n">
         <v>2.63</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>6.56</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42872.38541666666</v>
+        <v>42873.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>166.75</v>
+        <v>163.5</v>
       </c>
       <c r="I20" t="n">
         <v>164.1041410629085</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.11</v>
+        <v>-5.98</v>
       </c>
       <c r="L20" t="n">
-        <v>5.32</v>
+        <v>6.21</v>
       </c>
       <c r="M20" t="n">
         <v>0.21</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.07</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42944.38541666666</v>
+        <v>42947.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>148.85</v>
+        <v>153.1</v>
       </c>
       <c r="I21" t="n">
         <v>152.5387188102171</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K21" t="n">
-        <v>8.960000000000001</v>
+        <v>6.36</v>
       </c>
       <c r="L21" t="n">
         <v>1.93</v>
@@ -1638,7 +1889,7 @@
         <v>3.36</v>
       </c>
       <c r="N21" t="n">
-        <v>1.83</v>
+        <v>2.86</v>
       </c>
       <c r="O21" t="n">
         <v>-1.95</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>7.62</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42965.38541666666</v>
+        <v>42968.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>145.4</v>
+        <v>142.05</v>
       </c>
       <c r="I22" t="n">
         <v>142.399661278594</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.03</v>
+        <v>-7.22</v>
       </c>
       <c r="L22" t="n">
-        <v>6.43</v>
+        <v>7.71</v>
       </c>
       <c r="M22" t="n">
         <v>1.32</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>9.08</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>42997.38541666666</v>
+        <v>42998.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>149.95</v>
+        <v>151.6</v>
       </c>
       <c r="I23" t="n">
         <v>151.2847023797914</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.56</v>
+        <v>-6.72</v>
       </c>
       <c r="L23" t="n">
-        <v>6.86</v>
+        <v>8.76</v>
       </c>
       <c r="M23" t="n">
         <v>1.4</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.65</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43053.38541666666</v>
+        <v>43054.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>164.5</v>
+        <v>160.45</v>
       </c>
       <c r="I24" t="n">
         <v>163.89307252112</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K24" t="n">
-        <v>8.51</v>
+        <v>5.84</v>
       </c>
       <c r="L24" t="n">
         <v>3.99</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>10.61</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43090.38541666666</v>
+        <v>43091.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>169.95</v>
+        <v>174.8</v>
       </c>
       <c r="I25" t="n">
         <v>170.1219876255349</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.92</v>
+        <v>-8.94</v>
       </c>
       <c r="L25" t="n">
-        <v>7.63</v>
+        <v>9.16</v>
       </c>
       <c r="M25" t="n">
         <v>2.99</v>
       </c>
       <c r="N25" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="O25" t="n">
         <v>-2.46</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43132.38541666666</v>
+        <v>43133.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>176.15</v>
+        <v>174.15</v>
       </c>
       <c r="I26" t="n">
         <v>175.8285436403123</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K26" t="n">
-        <v>0.77</v>
+        <v>-0.37</v>
       </c>
       <c r="L26" t="n">
         <v>2.92</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.94</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43229.38541666666</v>
+        <v>43230.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>165.25</v>
+        <v>170.15</v>
       </c>
       <c r="I27" t="n">
         <v>169.6618574918194</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K27" t="n">
-        <v>5.11</v>
+        <v>2.3</v>
       </c>
       <c r="L27" t="n">
         <v>2.61</v>
@@ -1980,7 +2303,7 @@
         <v>2.48</v>
       </c>
       <c r="N27" t="n">
-        <v>2.48</v>
+        <v>2.97</v>
       </c>
       <c r="O27" t="n">
         <v>-1.14</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>7.57</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43242.38541666666</v>
+        <v>43243.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>167.35</v>
+        <v>158.45</v>
       </c>
       <c r="I28" t="n">
         <v>158.8020535746492</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.65</v>
+        <v>-6.88</v>
       </c>
       <c r="L28" t="n">
-        <v>6.64</v>
+        <v>7.41</v>
       </c>
       <c r="M28" t="n">
-        <v>0.12</v>
+        <v>0.66</v>
       </c>
       <c r="N28" t="n">
-        <v>1.91</v>
+        <v>5.32</v>
       </c>
       <c r="O28" t="n">
         <v>2.97</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>12.32</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43312.38541666666</v>
+        <v>43313.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>149.8</v>
+        <v>151.1</v>
       </c>
       <c r="I29" t="n">
         <v>150.631266158267</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K29" t="n">
-        <v>5.46</v>
+        <v>4.64</v>
       </c>
       <c r="L29" t="n">
         <v>5.71</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>7.73</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43377.38541666666</v>
+        <v>43378.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>155.85</v>
+        <v>132.9</v>
       </c>
       <c r="I30" t="n">
         <v>152.8940947955458</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K30" t="n">
-        <v>3.14</v>
+        <v>-12.05</v>
       </c>
       <c r="L30" t="n">
-        <v>2.81</v>
+        <v>12.94</v>
       </c>
       <c r="M30" t="n">
-        <v>0.96</v>
+        <v>7.19</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>14.73</v>
       </c>
       <c r="O30" t="n">
         <v>0.87</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>21.77</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43516</v>
+        <v>43517</v>
       </c>
       <c r="H31" t="n">
-        <v>130.2</v>
+        <v>132.8</v>
       </c>
       <c r="I31" t="n">
         <v>130.8357213531447</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>137.6145833333333</v>
+        <v>138.6145833333333</v>
       </c>
       <c r="K31" t="n">
-        <v>2.03</v>
+        <v>0.08</v>
       </c>
       <c r="L31" t="n">
         <v>13.77</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.25</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43644</v>
+        <v>43647</v>
       </c>
       <c r="H32" t="n">
-        <v>151.6</v>
+        <v>145.5</v>
       </c>
       <c r="I32" t="n">
         <v>147.0299691335078</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K32" t="n">
-        <v>14.16</v>
+        <v>9.56</v>
       </c>
       <c r="L32" t="n">
         <v>2.64</v>
@@ -2265,7 +2648,7 @@
         <v>2.39</v>
       </c>
       <c r="N32" t="n">
-        <v>3.37</v>
+        <v>4.02</v>
       </c>
       <c r="O32" t="n">
         <v>2</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.19</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H33" t="n">
-        <v>112.35</v>
+        <v>120.7</v>
       </c>
       <c r="I33" t="n">
         <v>118.8606032058614</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K33" t="n">
-        <v>22.78</v>
+        <v>17.04</v>
       </c>
       <c r="L33" t="n">
         <v>5.88</v>
@@ -2322,7 +2717,7 @@
         <v>1.63</v>
       </c>
       <c r="N33" t="n">
-        <v>5.16</v>
+        <v>7.43</v>
       </c>
       <c r="O33" t="n">
         <v>-4.02</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>16.03</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43784</v>
+        <v>43787</v>
       </c>
       <c r="H34" t="n">
-        <v>122.5</v>
+        <v>121</v>
       </c>
       <c r="I34" t="n">
         <v>121.3617570568924</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K34" t="n">
-        <v>1.49</v>
+        <v>0.25</v>
       </c>
       <c r="L34" t="n">
         <v>8.99</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43950</v>
+        <v>43951</v>
       </c>
       <c r="H35" t="n">
-        <v>63.7</v>
+        <v>72.25</v>
       </c>
       <c r="I35" t="n">
         <v>71.02326057664781</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K35" t="n">
-        <v>47.36</v>
+        <v>40.29</v>
       </c>
       <c r="L35" t="n">
         <v>1.65</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>23.07</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44021</v>
+        <v>44022</v>
       </c>
       <c r="H36" t="n">
-        <v>72.5</v>
+        <v>70.95</v>
       </c>
       <c r="I36" t="n">
         <v>72.46884534566377</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K36" t="n">
-        <v>0.35</v>
+        <v>-1.8</v>
       </c>
       <c r="L36" t="n">
         <v>10.52</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.91</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44145</v>
+        <v>44146</v>
       </c>
       <c r="H37" t="n">
-        <v>63.95</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="I37" t="n">
         <v>64.23386010039486</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K37" t="n">
-        <v>9.869999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="L37" t="n">
         <v>8.880000000000001</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.41</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H38" t="n">
-        <v>89.45</v>
+        <v>81.2</v>
       </c>
       <c r="I38" t="n">
         <v>81.78365548086977</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K38" t="n">
-        <v>36.88</v>
+        <v>24.25</v>
       </c>
       <c r="L38" t="n">
         <v>3.21</v>
@@ -2607,7 +3062,7 @@
         <v>0.54</v>
       </c>
       <c r="N38" t="n">
-        <v>2.51</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="O38" t="n">
         <v>2.19</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>20.54</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44208</v>
+        <v>44209</v>
       </c>
       <c r="H39" t="n">
-        <v>93.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I39" t="n">
         <v>93.88653863900134</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>-15.15</v>
+        <v>-17.12</v>
       </c>
       <c r="L39" t="n">
-        <v>16.32</v>
+        <v>20.07</v>
       </c>
       <c r="M39" t="n">
         <v>4.14</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44216</v>
+        <v>44217</v>
       </c>
       <c r="H40" t="n">
-        <v>89.34999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I40" t="n">
         <v>85.70632361104327</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.05</v>
+        <v>-9.99</v>
       </c>
       <c r="L40" t="n">
-        <v>8.779999999999999</v>
+        <v>10.83</v>
       </c>
       <c r="M40" t="n">
         <v>-0</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>14.99</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44242</v>
+        <v>44243</v>
       </c>
       <c r="H41" t="n">
-        <v>88.95</v>
+        <v>93.8</v>
       </c>
       <c r="I41" t="n">
         <v>91.25736790081557</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.91</v>
+        <v>-9.58</v>
       </c>
       <c r="L41" t="n">
-        <v>9.109999999999999</v>
+        <v>10.63</v>
       </c>
       <c r="M41" t="n">
         <v>1.93</v>
       </c>
       <c r="N41" t="n">
-        <v>4.56</v>
+        <v>5.45</v>
       </c>
       <c r="O41" t="n">
         <v>-4.2</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.34</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H42" t="n">
-        <v>94.65000000000001</v>
+        <v>92.25</v>
       </c>
       <c r="I42" t="n">
         <v>93.43535355439755</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K42" t="n">
-        <v>0.91</v>
+        <v>-1.65</v>
       </c>
       <c r="L42" t="n">
         <v>4.37</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>16.99</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44323</v>
+        <v>44326</v>
       </c>
       <c r="H43" t="n">
-        <v>100.7</v>
+        <v>102.95</v>
       </c>
       <c r="I43" t="n">
         <v>101.1891504403697</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K43" t="n">
-        <v>-9.16</v>
+        <v>-11.6</v>
       </c>
       <c r="L43" t="n">
-        <v>11.71</v>
+        <v>12.63</v>
       </c>
       <c r="M43" t="n">
         <v>2.81</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44393</v>
+        <v>44396</v>
       </c>
       <c r="H44" t="n">
-        <v>105.55</v>
+        <v>103.55</v>
       </c>
       <c r="I44" t="n">
         <v>104.8580343738805</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K44" t="n">
-        <v>2.53</v>
+        <v>0.58</v>
       </c>
       <c r="L44" t="n">
         <v>2.72</v>
       </c>
       <c r="M44" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="N44" t="n">
         <v>3.89</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44435</v>
+        <v>44438</v>
       </c>
       <c r="H45" t="n">
-        <v>105.4</v>
+        <v>108.6</v>
       </c>
       <c r="I45" t="n">
         <v>107.0554147016371</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.79</v>
+        <v>-4.88</v>
       </c>
       <c r="L45" t="n">
-        <v>3.43</v>
+        <v>5.07</v>
       </c>
       <c r="M45" t="n">
         <v>1.57</v>
       </c>
       <c r="N45" t="n">
-        <v>2.55</v>
+        <v>3.04</v>
       </c>
       <c r="O45" t="n">
         <v>-1.89</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>8.6</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44496</v>
+        <v>44497</v>
       </c>
       <c r="H46" t="n">
-        <v>142.7</v>
+        <v>135.75</v>
       </c>
       <c r="I46" t="n">
         <v>136.4452087922467</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K46" t="n">
-        <v>31.4</v>
+        <v>25</v>
       </c>
       <c r="L46" t="n">
         <v>2.85</v>
       </c>
       <c r="M46" t="n">
-        <v>2.16</v>
+        <v>5.01</v>
       </c>
       <c r="N46" t="n">
-        <v>4.58</v>
+        <v>4.87</v>
       </c>
       <c r="O46" t="n">
         <v>3.04</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>13.39</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H47" t="n">
-        <v>133.55</v>
+        <v>135.9</v>
       </c>
       <c r="I47" t="n">
         <v>134.4245664823633</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K47" t="n">
-        <v>1.62</v>
+        <v>-0.11</v>
       </c>
       <c r="L47" t="n">
         <v>8.029999999999999</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H48" t="n">
-        <v>145.3</v>
+        <v>141.55</v>
       </c>
       <c r="I48" t="n">
         <v>142.1424940865778</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K48" t="n">
-        <v>6.92</v>
+        <v>4.16</v>
       </c>
       <c r="L48" t="n">
         <v>2.02</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>12.76</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44624</v>
+        <v>44627</v>
       </c>
       <c r="H49" t="n">
-        <v>149.35</v>
+        <v>168.9</v>
       </c>
       <c r="I49" t="n">
         <v>158.5250797135811</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.51</v>
+        <v>-19.32</v>
       </c>
       <c r="L49" t="n">
-        <v>9.68</v>
+        <v>21.19</v>
       </c>
       <c r="M49" t="n">
         <v>3.29</v>
       </c>
       <c r="N49" t="n">
-        <v>4.55</v>
+        <v>13.09</v>
       </c>
       <c r="O49" t="n">
         <v>-2.58</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>17.5</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44679</v>
+        <v>44680</v>
       </c>
       <c r="H50" t="n">
-        <v>148.9</v>
+        <v>145</v>
       </c>
       <c r="I50" t="n">
         <v>147.2766547504975</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K50" t="n">
-        <v>-11.84</v>
+        <v>-14.15</v>
       </c>
       <c r="L50" t="n">
-        <v>13.8</v>
+        <v>14.65</v>
       </c>
       <c r="M50" t="n">
         <v>4.69</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>11.14</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44720</v>
+        <v>44721</v>
       </c>
       <c r="H51" t="n">
-        <v>147.65</v>
+        <v>149.65</v>
       </c>
       <c r="I51" t="n">
         <v>149.1534130077182</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.83</v>
+        <v>-3.21</v>
       </c>
       <c r="L51" t="n">
         <v>4.97</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>10.83</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44727</v>
+        <v>44728</v>
       </c>
       <c r="H52" t="n">
-        <v>136.85</v>
+        <v>129.75</v>
       </c>
       <c r="I52" t="n">
         <v>133.4459848568398</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K52" t="n">
-        <v>-8.550000000000001</v>
+        <v>-13.3</v>
       </c>
       <c r="L52" t="n">
-        <v>8.92</v>
+        <v>13.9</v>
       </c>
       <c r="M52" t="n">
         <v>1.55</v>
       </c>
       <c r="N52" t="n">
-        <v>3.06</v>
+        <v>5.19</v>
       </c>
       <c r="O52" t="n">
         <v>1.35</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>15.32</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44740</v>
+        <v>44741</v>
       </c>
       <c r="H53" t="n">
-        <v>134.95</v>
+        <v>139.25</v>
       </c>
       <c r="I53" t="n">
         <v>138.7101629269189</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.01</v>
+        <v>-7.32</v>
       </c>
       <c r="L53" t="n">
-        <v>5.66</v>
+        <v>9.67</v>
       </c>
       <c r="M53" t="n">
         <v>1.93</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>15.29</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44742</v>
+        <v>44743</v>
       </c>
       <c r="H54" t="n">
-        <v>137</v>
+        <v>118.45</v>
       </c>
       <c r="I54" t="n">
         <v>118.4902553932837</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.62</v>
+        <v>-14.94</v>
       </c>
       <c r="L54" t="n">
-        <v>5.1</v>
+        <v>15.62</v>
       </c>
       <c r="M54" t="n">
-        <v>0.68</v>
+        <v>1.75</v>
       </c>
       <c r="N54" t="n">
-        <v>1.62</v>
+        <v>13.54</v>
       </c>
       <c r="O54" t="n">
         <v>3.19</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
         <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>26.43</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44837</v>
+        <v>44838</v>
       </c>
       <c r="H55" t="n">
-        <v>119.65</v>
+        <v>121</v>
       </c>
       <c r="I55" t="n">
         <v>119.7940282774592</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.01</v>
+        <v>-2.15</v>
       </c>
       <c r="L55" t="n">
         <v>15.32</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.73</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44957</v>
+        <v>44958</v>
       </c>
       <c r="H56" t="n">
-        <v>130.95</v>
+        <v>130.4</v>
       </c>
       <c r="I56" t="n">
         <v>130.9258680016659</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K56" t="n">
-        <v>8.220000000000001</v>
+        <v>7.77</v>
       </c>
       <c r="L56" t="n">
         <v>6.03</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>6.83</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44972</v>
+        <v>44973</v>
       </c>
       <c r="H57" t="n">
-        <v>133.25</v>
+        <v>140.9</v>
       </c>
       <c r="I57" t="n">
         <v>138.3914419083267</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.19</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>3.53</v>
+        <v>8.4</v>
       </c>
       <c r="M57" t="n">
-        <v>0.61</v>
+        <v>1.73</v>
       </c>
       <c r="N57" t="n">
-        <v>1.61</v>
+        <v>5.74</v>
       </c>
       <c r="O57" t="n">
         <v>-0.42</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>9.4</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45076</v>
+        <v>45077</v>
       </c>
       <c r="H58" t="n">
-        <v>143.55</v>
+        <v>140</v>
       </c>
       <c r="I58" t="n">
         <v>143.4579523934335</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K58" t="n">
-        <v>1.88</v>
+        <v>-0.64</v>
       </c>
       <c r="L58" t="n">
         <v>6</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>5</v>
+      </c>
+      <c r="U58" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>7.64</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="H59" t="n">
-        <v>147.1</v>
+        <v>149.5</v>
       </c>
       <c r="I59" t="n">
         <v>147.455348193626</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.07</v>
+        <v>-6.79</v>
       </c>
       <c r="L59" t="n">
-        <v>6.11</v>
+        <v>7.04</v>
       </c>
       <c r="M59" t="n">
         <v>1.54</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.03</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H60" t="n">
-        <v>251.75</v>
+        <v>237.7</v>
       </c>
       <c r="I60" t="n">
         <v>240.7027998662251</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K60" t="n">
-        <v>68.39</v>
+        <v>59</v>
       </c>
       <c r="L60" t="n">
         <v>1.77</v>
@@ -3861,7 +4580,7 @@
         <v>2.09</v>
       </c>
       <c r="N60" t="n">
-        <v>5.02</v>
+        <v>5.58</v>
       </c>
       <c r="O60" t="n">
         <v>1.63</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>9</v>
+      </c>
+      <c r="U60" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>12.64</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="H61" t="n">
-        <v>263.25</v>
+        <v>266.3</v>
       </c>
       <c r="I61" t="n">
         <v>265.2269422362934</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K61" t="n">
-        <v>-10.75</v>
+        <v>-12.03</v>
       </c>
       <c r="L61" t="n">
-        <v>14.56</v>
+        <v>14.72</v>
       </c>
       <c r="M61" t="n">
         <v>1.25</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>6.33</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H62" t="n">
-        <v>257.7</v>
+        <v>246.9</v>
       </c>
       <c r="I62" t="n">
         <v>249.4356788126702</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.23</v>
+        <v>-7.29</v>
       </c>
       <c r="L62" t="n">
-        <v>4.92</v>
+        <v>8</v>
       </c>
       <c r="M62" t="n">
         <v>0.04</v>
       </c>
       <c r="N62" t="n">
-        <v>3.03</v>
+        <v>4.19</v>
       </c>
       <c r="O62" t="n">
         <v>1.16</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>12.05</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45477</v>
+        <v>45478</v>
       </c>
       <c r="H63" t="n">
-        <v>257.9</v>
+        <v>268.25</v>
       </c>
       <c r="I63" t="n">
         <v>263.4208528076455</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.46</v>
+        <v>-8.65</v>
       </c>
       <c r="L63" t="n">
-        <v>8.02</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M63" t="n">
         <v>5.14</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H64" t="n">
-        <v>288.75</v>
+        <v>284.9</v>
       </c>
       <c r="I64" t="n">
         <v>286.7474552767003</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K64" t="n">
-        <v>7.64</v>
+        <v>6.21</v>
       </c>
       <c r="L64" t="n">
         <v>4.04</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>15.21</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="H65" t="n">
-        <v>234.7</v>
+        <v>246.9</v>
       </c>
       <c r="I65" t="n">
         <v>238.7235722043395</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K65" t="n">
-        <v>17.62</v>
+        <v>13.34</v>
       </c>
       <c r="L65" t="n">
         <v>12.72</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>6</v>
+      </c>
+      <c r="U65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>9.34</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45695</v>
+        <v>45698</v>
       </c>
       <c r="H66" t="n">
-        <v>237.35</v>
+        <v>231.2</v>
       </c>
       <c r="I66" t="n">
         <v>234.7002729152383</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.87</v>
+        <v>-6.36</v>
       </c>
       <c r="L66" t="n">
-        <v>5.43</v>
+        <v>6.62</v>
       </c>
       <c r="M66" t="n">
         <v>1.25</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>11.3</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H67" t="n">
-        <v>231.15</v>
+        <v>232.55</v>
       </c>
       <c r="I67" t="n">
         <v>231.4753246176533</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K67" t="n">
-        <v>0.02</v>
+        <v>-0.58</v>
       </c>
       <c r="L67" t="n">
         <v>2.96</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>7.79</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H68" t="n">
-        <v>232.05</v>
+        <v>215.55</v>
       </c>
       <c r="I68" t="n">
         <v>219.9665127411365</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.22</v>
+        <v>-7.31</v>
       </c>
       <c r="L68" t="n">
-        <v>2.13</v>
+        <v>8.06</v>
       </c>
       <c r="M68" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="N68" t="n">
-        <v>2.93</v>
+        <v>7.11</v>
       </c>
       <c r="O68" t="n">
         <v>0.61</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>13.32</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45762</v>
+        <v>45763</v>
       </c>
       <c r="H69" t="n">
-        <v>221.9</v>
+        <v>230.05</v>
       </c>
       <c r="I69" t="n">
         <v>229.1368872117116</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.95</v>
+        <v>-6.73</v>
       </c>
       <c r="L69" t="n">
-        <v>6.73</v>
+        <v>7.05</v>
       </c>
       <c r="M69" t="n">
         <v>2.88</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>12.41</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="H70" t="n">
-        <v>229.85</v>
+        <v>225.85</v>
       </c>
       <c r="I70" t="n">
         <v>227.709381883002</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.09</v>
+        <v>-1.83</v>
       </c>
       <c r="L70" t="n">
         <v>5.3</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>5</v>
+      </c>
+      <c r="U70" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>4.91</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="H71" t="n">
-        <v>228.4</v>
+        <v>231.8</v>
       </c>
       <c r="I71" t="n">
         <v>231.2353159019968</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.13</v>
+        <v>-2.63</v>
       </c>
       <c r="L71" t="n">
-        <v>2.39</v>
+        <v>3.98</v>
       </c>
       <c r="M71" t="n">
         <v>0.93</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>4.72</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="H72" t="n">
-        <v>232.55</v>
+        <v>229.95</v>
       </c>
       <c r="I72" t="n">
         <v>232.4143307294743</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K72" t="n">
-        <v>0.32</v>
+        <v>-0.8</v>
       </c>
       <c r="L72" t="n">
-        <v>1.9</v>
+        <v>3.08</v>
       </c>
       <c r="M72" t="n">
         <v>0.6</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>4.6</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="H73" t="n">
-        <v>230.3</v>
+        <v>238.2</v>
       </c>
       <c r="I73" t="n">
         <v>237.6883355538628</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.15</v>
+        <v>-3.59</v>
       </c>
       <c r="L73" t="n">
         <v>4.87</v>
@@ -4602,7 +5477,7 @@
         <v>2.23</v>
       </c>
       <c r="N73" t="n">
-        <v>2.42</v>
+        <v>3.43</v>
       </c>
       <c r="O73" t="n">
         <v>-1.12</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="H74" t="n">
-        <v>264.1</v>
+        <v>260.45</v>
       </c>
       <c r="I74" t="n">
         <v>262.4719614653465</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K74" t="n">
-        <v>10.87</v>
+        <v>9.34</v>
       </c>
       <c r="L74" t="n">
         <v>3.27</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,25 +5594,25 @@
         <v>10.43</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="H75" t="n">
-        <v>284.65</v>
+        <v>288.05</v>
       </c>
       <c r="I75" t="n">
         <v>287.0352692324831</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K75" t="n">
-        <v>-9.289999999999999</v>
+        <v>-10.6</v>
       </c>
       <c r="L75" t="n">
-        <v>10.71</v>
+        <v>12.5</v>
       </c>
       <c r="M75" t="n">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="N75" t="n">
         <v>4.35</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>8.73</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H76" t="n">
-        <v>289.95</v>
+        <v>280.8</v>
       </c>
       <c r="I76" t="n">
         <v>283.2365314417798</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K76" t="n">
-        <v>0.66</v>
+        <v>-2.52</v>
       </c>
       <c r="L76" t="n">
         <v>4.62</v>
@@ -4773,7 +5684,7 @@
         <v>2.32</v>
       </c>
       <c r="N76" t="n">
-        <v>2.22</v>
+        <v>3.16</v>
       </c>
       <c r="O76" t="n">
         <v>1.19</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>9.73</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="H77" t="n">
-        <v>297.15</v>
+        <v>300.9</v>
       </c>
       <c r="I77" t="n">
         <v>300.5291739221442</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K77" t="n">
-        <v>-5.82</v>
+        <v>-7.16</v>
       </c>
       <c r="L77" t="n">
-        <v>6.91</v>
+        <v>8.16</v>
       </c>
       <c r="M77" t="n">
         <v>2.1</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>7.67</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="H78" t="n">
-        <v>287.5</v>
+        <v>274.05</v>
       </c>
       <c r="I78" t="n">
         <v>278.7961514896812</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K78" t="n">
-        <v>-4.45</v>
+        <v>-8.92</v>
       </c>
       <c r="L78" t="n">
-        <v>5.62</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M78" t="n">
-        <v>0.71</v>
+        <v>1.15</v>
       </c>
       <c r="N78" t="n">
-        <v>1.98</v>
+        <v>4.68</v>
       </c>
       <c r="O78" t="n">
         <v>1.26</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>9.94</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="H79" t="n">
-        <v>249.89</v>
+        <v>251.9</v>
       </c>
       <c r="I79" t="n">
         <v>250.6704852436521</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K79" t="n">
-        <v>8.82</v>
+        <v>8.08</v>
       </c>
       <c r="L79" t="n">
         <v>3.7</v>
@@ -4953,7 +5900,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>5.26</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="H80" t="n">
-        <v>248.76</v>
+        <v>238.56</v>
       </c>
       <c r="I80" t="n">
         <v>240.8988842354253</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.25</v>
+        <v>-5.3</v>
       </c>
       <c r="L80" t="n">
-        <v>1.44</v>
+        <v>5.46</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="N80" t="n">
-        <v>1.43</v>
+        <v>4.1</v>
       </c>
       <c r="O80" t="n">
         <v>0.8</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,14 @@
       <c r="Q81" t="n">
         <v>65</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10019,7 +10998,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51.9</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="6">
@@ -10029,7 +11008,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -10039,7 +11018,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8">
@@ -10049,7 +11028,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -10059,7 +11038,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67.5</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="10">
@@ -10069,7 +11048,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>119.8</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="11">
@@ -10109,7 +11088,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.35</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="15">
@@ -10119,7 +11098,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.62</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="16">
@@ -10129,7 +11108,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.04</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="17">
@@ -10139,7 +11118,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>68.39</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
@@ -10149,7 +11128,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.8</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="19">
@@ -10159,7 +11138,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.1</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="20">
@@ -10169,7 +11148,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.66</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="21">
@@ -10179,7 +11158,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.32</v>
+        <v>21.19</v>
       </c>
     </row>
     <row r="22">
@@ -10189,7 +11168,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
@@ -10199,7 +11178,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -10209,7 +11188,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="25">
@@ -10219,7 +11198,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.17</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="26">
@@ -10229,7 +11208,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.02</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="27">
@@ -10249,7 +11228,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
